--- a/mode_docx_gen/part/lvrbvtr1/RVTR1.xlsx
+++ b/mode_docx_gen/part/lvrbvtr1/RVTR1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.11.240\Company\Ivanovo\Документация ЮНИТ М300\Разработка\Схемы ФБ ЮНИТ-М3\Трансформатор\ИЭУ Т 35 кВ Россети\01. Разработка ФБ\28. КЦН НН\_xlsx\funcs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\www_obj\mode_docx_gen\part\lvrbvtr1\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A08608-C078-4A0C-A698-472AA77F2C4B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26820" windowHeight="9060" activeTab="1"/>
+    <workbookView xWindow="38280" yWindow="2325" windowWidth="15600" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Signals" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="109">
   <si>
     <t>Категория (group)</t>
   </si>
@@ -256,12 +257,6 @@
     <t>ING</t>
   </si>
   <si>
-    <t>КЦН НН</t>
-  </si>
-  <si>
-    <t>LVRBVTR</t>
-  </si>
-  <si>
     <t>LVRVTR</t>
   </si>
   <si>
@@ -326,12 +321,39 @@
   </si>
   <si>
     <t>Сигнализация неисправности цепей напряжения</t>
+  </si>
+  <si>
+    <t>Режим пуска</t>
+  </si>
+  <si>
+    <t>Реж_пуска</t>
+  </si>
+  <si>
+    <t>SGF2</t>
+  </si>
+  <si>
+    <t>0 - Внутренний, 1 - Внешний</t>
+  </si>
+  <si>
+    <t>КЦН НН1</t>
+  </si>
+  <si>
+    <t>LVRBVTR1</t>
+  </si>
+  <si>
+    <t>alias</t>
+  </si>
+  <si>
+    <t>Umin</t>
+  </si>
+  <si>
+    <t>U2max</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -348,7 +370,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,8 +383,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -398,11 +426,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -410,8 +449,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -718,8 +761,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -733,7 +776,7 @@
     <col min="28" max="28" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -824,13 +867,16 @@
       <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="6" t="s">
+        <v>106</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>34</v>
@@ -863,7 +909,7 @@
         <v>31</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>37</v>
@@ -905,7 +951,7 @@
         <v>0</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AB2" s="3" t="s">
         <v>43</v>
@@ -917,12 +963,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>44</v>
@@ -955,7 +1001,7 @@
         <v>31</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>37</v>
@@ -997,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AB3" s="3" t="s">
         <v>47</v>
@@ -1009,12 +1055,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>55</v>
@@ -1047,7 +1093,7 @@
         <v>31</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>31</v>
@@ -1101,12 +1147,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>57</v>
@@ -1139,7 +1185,7 @@
         <v>31</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>31</v>
@@ -1193,21 +1239,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>31</v>
@@ -1231,10 +1277,10 @@
         <v>31</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>38</v>
@@ -1273,10 +1319,10 @@
         <v>1</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AC6" s="3" t="s">
         <v>31</v>
@@ -1285,21 +1331,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>31</v>
@@ -1323,10 +1369,10 @@
         <v>31</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>38</v>
@@ -1365,11 +1411,11 @@
         <v>1</v>
       </c>
       <c r="AA7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB7" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="AB7" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="AC7" s="3" t="s">
         <v>31</v>
       </c>
@@ -1377,12 +1423,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>53</v>
@@ -1415,7 +1461,7 @@
         <v>31</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>31</v>
@@ -1469,21 +1515,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>31</v>
@@ -1507,10 +1553,10 @@
         <v>31</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>38</v>
@@ -1549,10 +1595,10 @@
         <v>1</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AC9" s="3" t="s">
         <v>31</v>
@@ -1561,24 +1607,24 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>32</v>
@@ -1599,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>31</v>
@@ -1653,113 +1699,113 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:31" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I11" s="3">
-        <v>2</v>
-      </c>
-      <c r="J11" s="3">
+      <c r="B11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="K11" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="L11" s="3">
-        <v>6</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="T11" s="3">
-        <v>0</v>
-      </c>
-      <c r="U11" s="3">
-        <v>0</v>
-      </c>
-      <c r="V11" s="3">
-        <v>0</v>
-      </c>
-      <c r="W11" s="3">
-        <v>0</v>
-      </c>
-      <c r="X11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD11" s="3" t="s">
+      <c r="D11" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>1</v>
+      </c>
+      <c r="K11" s="5">
+        <v>1</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="R11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
+        <v>0</v>
+      </c>
+      <c r="W11" s="5">
+        <v>0</v>
+      </c>
+      <c r="X11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD11" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>31</v>
@@ -1768,13 +1814,13 @@
         <v>48</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I12" s="3">
         <v>2</v>
       </c>
       <c r="J12" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K12" s="3">
         <v>0.1</v>
@@ -1783,7 +1829,7 @@
         <v>6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>49</v>
@@ -1825,10 +1871,10 @@
         <v>0</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>31</v>
@@ -1836,55 +1882,58 @@
       <c r="AD12" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="AE12" s="3" t="s">
+        <v>107</v>
+      </c>
     </row>
-    <row r="13" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>76</v>
+        <v>48</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="I13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" s="3">
-        <v>100000</v>
+        <v>50</v>
       </c>
       <c r="K13" s="3">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="L13" s="3">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>31</v>
@@ -1917,20 +1966,118 @@
         <v>0</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="AD13" s="3" t="s">
         <v>31</v>
+      </c>
+      <c r="AE13" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>100000</v>
+      </c>
+      <c r="K14" s="3">
+        <v>10</v>
+      </c>
+      <c r="L14" s="3">
+        <v>500</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:AD24">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD24">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1939,7 +2086,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1959,7 +2106,7 @@
         <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1967,7 +2114,7 @@
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1977,15 +2124,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" t="s">
         <v>99</v>
-      </c>
-      <c r="B5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B6">
         <v>10</v>
